--- a/02_DIA_inicio_2026_analisis_assets/rbd_9586_liceo-araucania_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9586_liceo-araucania_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C61474D-9C96-4F7A-988B-F24060F728D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60ACC797-CFC6-4414-8B21-186346D9EE1B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0AF0F27-E2BD-4804-8EAC-917BAA27955E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{094CEC4C-660E-431E-BC90-F66E96C8E644}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{638CF382-E565-4A3D-9099-54333DBF52A0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EF85770-193F-48EC-9092-4FDCD86D4331}"/>
 </file>